--- a/data/trans_bre/POLIPATOLOGIA_Lim_2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_2-Clase-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 5,23</t>
+          <t>-4,9; 5,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 6,45</t>
+          <t>-4,17; 6,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 14,25</t>
+          <t>5,78; 14,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-35,43; 56,43</t>
+          <t>-34,73; 58,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,69; 63,29</t>
+          <t>-29,06; 69,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,26; 128,12</t>
+          <t>36,74; 126,63</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 11,24</t>
+          <t>0,18; 11,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 7,84</t>
+          <t>-2,79; 7,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 16,11</t>
+          <t>6,63; 16,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 103,93</t>
+          <t>-0,33; 107,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 80,57</t>
+          <t>-17,83; 84,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,5; 122,07</t>
+          <t>36,45; 123,57</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 13,17</t>
+          <t>-0,01; 14,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 24,08</t>
+          <t>7,74; 24,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,66; 40,92</t>
+          <t>19,08; 39,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 64,39</t>
+          <t>-0,04; 70,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,84; 159,73</t>
+          <t>42,22; 166,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>92,2; 804,81</t>
+          <t>95,8; 832,01</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 5,07</t>
+          <t>-2,56; 5,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 6,8</t>
+          <t>-0,95; 7,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 7,64</t>
+          <t>-11,57; 7,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 27,69</t>
+          <t>-11,8; 27,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 46,67</t>
+          <t>-5,3; 47,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 35,05</t>
+          <t>-45,79; 34,79</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,55; 23,07</t>
+          <t>13,01; 23,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,42; 18,64</t>
+          <t>9,17; 18,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 18,51</t>
+          <t>3,93; 19,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62,25; 146,58</t>
+          <t>59,58; 148,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>40,77; 102,11</t>
+          <t>41,14; 102,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,98; 85,87</t>
+          <t>16,52; 89,17</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29,77; 38,2</t>
+          <t>30,26; 38,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,74; 31,81</t>
+          <t>24,77; 31,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,11; 32,03</t>
+          <t>18,38; 32,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>385,84; 3137,45</t>
+          <t>453,18; 3169,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>486,48; 2279,43</t>
+          <t>504,47; 2318,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>97,6; 550,36</t>
+          <t>97,02; 599,27</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,25; 14,28</t>
+          <t>10,1; 14,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,75; 12,69</t>
+          <t>8,55; 12,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,22; 16,83</t>
+          <t>7,47; 16,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56,56; 89,88</t>
+          <t>56,39; 87,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>55,33; 88,98</t>
+          <t>53,42; 88,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,26; 122,55</t>
+          <t>45,81; 121,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_Lim_2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_2-Clase-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,22</t>
+          <t>10,02</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>74,71%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 5,71</t>
+          <t>-4,93; 5,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 6,52</t>
+          <t>-3,21; 6,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,78; 14,23</t>
+          <t>5,65; 14,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 58,66</t>
+          <t>-37,26; 53,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 69,34</t>
+          <t>-23,23; 66,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,74; 126,63</t>
+          <t>34,92; 123,43</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,46</t>
+          <t>12,66</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>85,03%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 11,76</t>
+          <t>0,26; 11,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 7,83</t>
+          <t>-2,36; 7,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 16,25</t>
+          <t>7,85; 17,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 107,44</t>
+          <t>1,52; 107,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 84,07</t>
+          <t>-18,1; 82,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,45; 123,57</t>
+          <t>44,16; 137,73</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27,42</t>
+          <t>20,55</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>228,17%</t>
+          <t>113,08%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 14,04</t>
+          <t>-0,23; 14,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 24,82</t>
+          <t>8,06; 23,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,08; 39,88</t>
+          <t>13,89; 27,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 70,14</t>
+          <t>-1,86; 68,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,22; 166,49</t>
+          <t>43,6; 163,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>95,8; 832,01</t>
+          <t>69,83; 171,2</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>6,84</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 5,04</t>
+          <t>-2,41; 5,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 7,12</t>
+          <t>-0,66; 6,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 7,59</t>
+          <t>3,13; 10,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 27,92</t>
+          <t>-11,71; 28,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 47,39</t>
+          <t>-3,92; 43,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,79; 34,79</t>
+          <t>13,14; 50,82</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,58</t>
+          <t>18,3</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>85,26%</t>
         </is>
       </c>
     </row>
@@ -954,39 +954,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,01; 23,22</t>
+          <t>13,17; 23,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,17; 18,29</t>
+          <t>9,3; 18,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 19,51</t>
+          <t>13,73; 22,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,58; 148,35</t>
+          <t>63,11; 146,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,14; 102,54</t>
+          <t>40,5; 105,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,52; 89,17</t>
+          <t>56,29; 119,02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26,52</t>
+          <t>25,88</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>271,36%</t>
+          <t>263,86%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30,26; 38,38</t>
+          <t>30,33; 38,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,77; 31,87</t>
+          <t>24,77; 31,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,38; 32,16</t>
+          <t>18,29; 31,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>453,18; 3169,48</t>
+          <t>475,84; 3179,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>504,47; 2318,98</t>
+          <t>467,6; 2328,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>97,02; 599,27</t>
+          <t>106,6; 566,09</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12,82</t>
+          <t>14,38</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,1; 14,18</t>
+          <t>10,14; 14,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,55; 12,57</t>
+          <t>8,63; 12,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,47; 16,82</t>
+          <t>12,56; 16,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56,39; 87,81</t>
+          <t>56,53; 90,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>53,42; 88,7</t>
+          <t>54,78; 88,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,81; 121,39</t>
+          <t>65,01; 94,27</t>
         </is>
       </c>
     </row>
